--- a/artfynd/A 28408-2019 artfynd.xlsx
+++ b/artfynd/A 28408-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28408-2019 artfynd.xlsx
+++ b/artfynd/A 28408-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,132 +1378,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>86555940</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Myrorna, N om (*knärot* /stjälk/), Upl</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>703206.7403017445</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6626265.149522305</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Frötuna</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>AB-Nor-1742</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2018-04-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2018-04-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Obs: Flera dellokaler. Se privata obsar! Myrorna, N om, Obskoord: 6626090/1658024/10 m (). Enstaka fynd. Gammal barrblandskog. Delvis fuktdråg och kalkpåverkad mark.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kjell  Andersson, Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
